--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_01_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_01_20_Cau.xlsx
@@ -1419,13 +1419,17 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>9.56</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>60</v>
@@ -1433,7 +1437,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>P=1−(1−0,01)^10=1−0,99^10≈9,56%.</t>
+          <t>Xác suất gặp ít nhất một lượt latency &gt; 5s trong 10 lượt chat độc lập: P = 1 - (1 - 0,01)^10 = 1 - 0,99^10 ≈ 0,0956178... = 9,56%.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_01_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_01_20_Cau.xlsx
@@ -672,10 +672,21 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Predefined indicator, Known failure mode.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Predefined indicator, Known failure mode.</t>
+- 1.0đ: Phân loại chính xác 'queue depth &gt; 100' là Monitoring (ngưỡng định trước, known failure mode).
+- 1.0đ: Phân loại chính xác incident tenant A dùng tool X là Observability (suy luận trạng thái nội tại, unknown-unknowns).
+- 1.0đ: Nêu rõ các signal còn thiếu: high-cardinality tags (`tenant_id`, `tool_name`), tool payload logs, và tenant configuration metadata.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại theo nguyên lý vận hành:
+- Điều kiện 'queue depth &gt; 100' thuộc về **Monitoring**: Đây là việc giám sát một chỉ số tổng hợp định trước (predefined metric) với ngưỡng cố định (threshold) nhằm cảnh báo các chế độ lỗi đã biết (known failure modes / known-knowns) về tình trạng tắc nghẽn hàng đợi.
+- Incident 'chỉ tenant A bị sai output khi dùng tool X' thuộc về **Observability**: Đây là hành vi điều tra trạng thái nội tại của hệ thống cho một sự cố dị biệt, chưa từng lường trước (unknown-unknowns) chỉ xảy ra ở một tập con dữ liệu có độ phân giải cao (high-cardinality slice).
+2. Signal còn thiếu cho incident lạ:
+- Cần bổ sung distributed tracing có gắn high-cardinality attributes: `tenant_id = 'tenant_A'`, `tool_name = 'tool_X'`, `schema_version`, và `execution_context`.
+- Structured logs chi tiết của Tool X: ghi nhận sanitized input arguments, raw response payload, execution error/exit code, và latency của lời gọi tool.
+- Metadata cấu hình tenant: feature flags, quyền hạn tài khoản (RBAC/permissions), hoặc quota/rate-limits riêng của tenant A đối với API phụ thuộc của Tool X.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Monitoring giải quyết câu hỏi 'Hệ thống có đang hoạt động bình thường không?' dựa trên các quy tắc xác định từ trước. Trong khi đó, Observability giải quyết câu hỏi 'Tại sao sự cố này xảy ra?' đối với các trạng thái mới lạ mà không cần deploy thêm code. Để gỡ lỗi vấn đề khu biệt ở một tenant cụ thể khi gọi một công cụ cụ thể, hệ thống bắt buộc phải thu thập telemetry có tính phân giải cao (high cardinality) kết hợp ngữ cảnh phân tán (distributed tracing span) thay vì chỉ dựa vào metric hàng đợi tổng hợp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Monitoring Distributed Systems (https://sre.google/sre-book/monitoring-distributed-systems/) &amp; Honeycomb Observability Engineering (https://www.honeycomb.io/observability-engineering-oreilly-book)</t>
         </is>
       </c>
     </row>
@@ -802,10 +813,24 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Correctness dù status success, Work tính tiền theo token.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Correctness dù status success, Work tính tiền theo token.</t>
+- 1.0đ: Nêu câu hỏi quan sát và bằng chứng định lượng rõ ràng cho Retrieval Failure (empty-result rate, similarity scores, chunk evidence).
+- 1.0đ: Nêu câu hỏi quan sát và bằng chứng định lượng rõ ràng cho Quality Failure (user regenerate rate, groundedness score, qualitative traces).
+- 1.0đ: Nêu câu hỏi quan sát và bằng chứng định lượng rõ ràng cho Cost/Runtime Failure (token consumption per task, latency impact, billing trend).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Ba observable questions và bằng chứng (evidence) tương ứng để phân biệt 3 loại lỗi:
+1. Phân biệt **Retrieval Failure**:
+- Observable Question: 'Tỷ lệ truy vấn trả về rỗng (empty retrieval rate) và điểm tương đồng ngữ nghĩa (semantic relevance) giữa prompt và các retrieved chunks từ corpus mới là bao nhiêu?'
+- Evidence: Metric `retrieval_empty_result_count` tăng đột biến; phân phối điểm similarity score nằm dưới ngưỡng 0.6; trace logs cho thấy retriever trả về mảng rỗng `[]` hoặc chunks không chứa từ khóa mục tiêu.
+2. Phân biệt **Quality Failure**:
+- Observable Question: 'Tỷ lệ người dùng bấm nút regenerate hoặc đánh giá thumbs-down tăng lên do câu trả lời bị hallucinated hay không giải quyết được nhu cầu?'
+- Evidence: Metric `user_regenerate_rate` tăng cao trên cùng một `session_id`; điểm groundedness/faithfulness qua online eval giảm sâu; model output sinh ra các câu xin lỗi hoặc nội dung thoái thác chung chung.
+3. Phân biệt **Cost / Runtime Failure**:
+- Observable Question: 'Việc regenerate và truy vấn rỗng có dẫn đến bùng nổ token sử dụng, kéo dài thời gian phản hồi hoặc kích hoạt vòng lặp retry tốn kém không?'
+- Evidence: Tổng số token tiêu thụ trên mỗi session (`total_tokens_per_session`) tăng gấp 2-3 lần; hóa đơn tính phí API tăng không tương xứng với lượng người dùng; P95 latency tăng do agent thực hiện fallback re-prompting.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong hệ thống AI/Agentic, mã trạng thái HTTP 200 (error rate 0%) che giấu các lỗi suy thoái chất lượng âm thầm (silent failures). Cần phân lập rõ ba lớp: Retrieval (lớp thu thập tri thức), Quality (lớp suy luận và độ chính xác nội dung của LLM), và Cost/Runtime (tài nguyên hạ tầng và chi phí token) để xác định đúng nguyên nhân gốc thay vì chỉ nhìn vào chỉ số sẵn sàng của API.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Arize AI Documentation: LLM Observability &amp; Failure Modes (https://docs.arize.com/arize/llm-evaluation-and-observability) &amp; TruLens RAG Triad (https://www.trulens.org/trulens_eval/core_concepts_rag_triad/)</t>
         </is>
       </c>
     </row>
@@ -884,10 +909,23 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Observe-analyze-act, So với objective.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Observe-analyze-act, So với objective.</t>
+- 1.0đ: Phân tích chuẩn xác điểm yếu ở khâu Triage &amp; Fix (MTTD giảm nhưng MTTR 50 phút do thiếu diagnostic context).
+- 1.0đ: Chỉ ra điểm yếu ở khâu Post-mitigation Verification (chỉ xem dashboard 1 lần là đứt gãy feedback loop).
+- 1.0đ: Thiết kế cơ chế theo dõi hồi phục liên tục (continuous rolling telemetry, burn rate monitor sau fix).
+- 1.0đ: Đưa ra giải pháp nâng cấp alert payload (deep links, runbook, filtered traces) và giám sát tác động phụ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá stage yếu trong chu trình phản hồi (Observability Feedback Loop):
+- Chu trình phản hồi gồm: Detect (Phát hiện) -&gt; Triage (Chẩn đoán) -&gt; Remediate/Fix (Khắc phục) -&gt; Verify/Observe (Xác nhận sau can thiệp).
+- **Stage yếu 1: Triage &amp; Fix (Chẩn đoán và khắc phục)**: Dù thời gian phát hiện (MTTD) giảm từ 20 xuống 4 phút, nhưng thời gian sửa (MTTR) vẫn mất 50 phút. Điều này chứng minh alert hiện tại chỉ là cảnh báo triệu chứng (symptom alert) mà thiếu dữ liệu ngữ cảnh (contextual traces/logs) và runbook hành động, buộc kỹ sư phải điều tra thủ công tốn thời gian.
+- **Stage yếu 2: Post-mitigation Verification (Kiểm chứng sau sửa)**: Việc đội ngũ 'chỉ xem dashboard một lần' sau khi can thiệp là hành vi đứt gãy vòng phản hồi; nguy cơ cao là can thiệp chưa dứt điểm, gây ra hồi quy (regression) hoặc hiệu ứng phụ ở downstream service.
+2. Thiết kế observation tiếp theo:
+- **Continuous Recovery Tracking**: Theo dõi SLI chính (P95 latency, error rate) và burn rate trong các cửa sổ trượt (rolling windows) 5m, 15m, 1h sau khi fix để xác nhận hệ thống duy trì baseline ổn định.
+- **Diagnostic Alert Payload Enrichment**: Nhúng trực tiếp deep-link trỏ tới Jaeger trace waterfall và Loki log queries đã filter sẵn theo correlation ID vào thông báo alert để rút ngắn thời gian chẩn đoán.
+- **Secondary Impact Telemetry**: Giám sát các chỉ số liên đới như queue drain rate, database connection pool, và worker saturation để đảm bảo việc giải phóng tải sau sự cố không làm sập hạ tầng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên lý OODA loop và closed-loop SRE: Một hệ thống cảnh báo tốt không chỉ phát hiện sớm mà phải hỗ trợ rút ngắn toàn bộ chu trình từ chẩn đoán đến phục hồi. Nếu chỉ tối ưu Detection mà không cải thiện công cụ chẩn đoán (Triage context) và thiếu quy trình kiểm chứng liên tục sau khắc phục (Continuous verification), tổng thời gian gián đoạn dịch vụ vẫn không giảm đáng kể và rủi ro tái phát sự cố luôn ở mức cao.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Incident Management (https://sre.google/sre-book/incident-management/) &amp; Charity Majors: The Observability Engineering Feedback Loop</t>
         </is>
       </c>
     </row>
@@ -966,10 +1004,25 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Aggregate metric, Detailed event log.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Aggregate metric, Detailed event log.</t>
+- 1.0đ: Chọn Metrics cho Cohort và giải thích rõ giới hạn của Metrics (thiếu payload chi tiết, không giải thích nguyên nhân từng ca).
+- 1.0đ: Chọn Logs cho Request lỗi và giải thích rõ giới hạn của Logs (thiếu ngữ cảnh phân tán, không đo được critical path xuyên service).
+- 1.0đ: Chọn Traces cho Critical path và giải thích rõ giới hạn của Traces (chỉ là mẫu đơn lẻ, chưa chứng minh mức độ phổ biến tổng thể).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Pillar cho từng bước điều tra:
+- **Bước 1: Xác định Cohort nào bị ảnh hưởng -&gt; Chọn Pillar: Metrics (Time-series Aggregates)**.
+  Sử dụng Prometheus metrics có gắn labels để nhóm tỷ lệ lỗi: `sum(rate(http_requests_total{status=~'5..'}[5m])) by (tenant_tier, client_version, region)`.
+- **Bước 2: Xác định Request cụ thể nào lỗi -&gt; Chọn Pillar: Logs (Structured Event Logs)**.
+  Sử dụng Elasticsearch/Loki truy vấn log mức `ERROR` quanh mốc 10:00: lọc theo cohort tìm được ở bước 1 để trích xuất stack trace, request parameters, và correlation ID.
+- **Bước 3: Xác định Dependency nào tạo critical path -&gt; Chọn Pillar: Distributed Traces (Traces / Spans)**.
+  Sử dụng Jaeger/Tempo xem biểu đồ trace waterfall của request lỗi, kiểm tra thời gian thực thi (span duration) và thứ tự gọi qua Database, LLM API, và Cache để tìm nút thắt cổ chai trên đường găng.
+2. Điều mỗi pillar CHƯA chứng minh được (Blind spots):
+- **Metrics**: Chỉ cung cấp con số tổng hợp thống kê; chưa chứng minh được nguyên nhân lỗi cụ thể của từng request và không hiển thị payload gây lỗi.
+- **Logs**: Chỉ cung cấp góc nhìn cục bộ rời rạc tại từng thời điểm của một service; chưa chứng minh được mối liên hệ phụ thuộc phân tán xuyên suốt các service và không chỉ ra được độ trễ đường găng.
+- **Traces**: Cho thấy thời gian và đường đi của một vài request mẫu; chưa chứng minh được mức độ phổ biến của lỗi trên toàn bộ hệ sinh thái nếu không được đối chiếu với tỷ lệ thống kê từ metrics.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Ba trụ cột của Observability (Metrics, Logs, Traces) có vai trò bổ trợ lẫn nhau và mỗi trụ cột đều có giới hạn riêng. Metrics trả lời câu hỏi 'Có điều gì bất thường và ở phân khúc nào?', Logs trả lời 'Chi tiết cụ thể của sự kiện lỗi là gì?', còn Traces trả lời 'Sự kiện đó diễn ra ở đâu trong hành trình phân tán và đâu là mắt xích nghẽn'. Kỹ sư SRE cần kết hợp tuần tự cả ba để tránh kết luận vội vàng dựa trên một góc nhìn phiến diện.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Specification: Overview and Signals (https://opentelemetry.io/docs/concepts/signals/) &amp; Peter Bourgon: Metrics, Tracing, and Logging</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1101,25 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra HTTP success khác correctness, Output quality chưa chứng minh.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra HTTP success khác correctness, Output quality chưa chứng minh.</t>
+- 1.0đ: Phân tích được sự bất lực của 3 pillar truyền thống đối với lỗi sai ngữ nghĩa (semantic failure dù HTTP 200).
+- 1.0đ: Thiết kế kiến trúc Online Evaluation bất đồng bộ (async queue, eval worker, low overhead).
+- 1.0đ: Nêu rõ các metric chất lượng ngữ nghĩa cụ thể (faithfulness, contradiction rate, unsupported claims) và tín hiệu feedback.
+- 1.0đ: Thiết lập Quality SLI và cơ chế phản ứng tự động (alerting, automated canary rollback/fallback).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Hạn chế của 3 pillar truyền thống:
+Metrics (HTTP 200, throughput), Logs (không có unhandled exception), và Traces (latency bình thường) hoàn toàn 'mù' trước chất lượng ngữ nghĩa (semantic correctness). Hệ thống vận hành hạ tầng hoàn hảo nhưng vẫn có thể cung cấp nội dung sai lệch điều khoản pháp lý nghiêm trọng.
+2. Thiết kế Quan sát Chất lượng (Online Eval - Trụ cột thứ tư):
+- **Asynchronous Eval Pipeline**: Thiết lập worker bất đồng bộ lắng nghe các cặp input-output từ Kafka/event bus để đánh giá mà không làm tăng độ trễ phục vụ người dùng.
+- **Chỉ số đánh giá ngữ nghĩa chuyên biệt (Semantic Metrics)**:
+  + `faithfulness_score` / `groundedness_score`: Sử dụng LLM-as-a-Judge hoặc mô hình NLI (Natural Language Inference) nhỏ để kiểm tra xem câu trả lời có được suy diễn hoàn toàn từ văn bản điều khoản pháp lý trong context hay không.
+  + `contradiction_rate`: Phát hiện các câu trả lời trực tiếp mâu thuẫn với điều khoản loại trừ trách nhiệm hoặc chính sách thanh toán.
+  + `unsupported_claim_count`: Đếm số lượng khẳng định trong câu trả lời không có trích dẫn (citation) hợp lệ.
+- **Implicit &amp; Explicit Telemetry**: Bổ sung telemetry người dùng: tỷ lệ thumbs-down gắn tag 'sai điều khoản', tỷ lệ copy text sau phản hồi, và tỷ lệ escalation chuyển tiếp sang nhân viên hỗ trợ con người.
+- **Quality Alerting &amp; Automated Guard**: Đặt Quality SLI: tỷ lệ câu trả lời vi phạm điều khoản pháp lý phải &lt; 0.5%. Khi vi phạm vượt ngưỡng trong cửa sổ 15m, kích hoạt PagerDuty và tự động kích hoạt chế độ fallback về prompt ổn định trước đó.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trụ cột thứ tư của Observability cho GenAI là Semantic Evaluation (Đánh giá ngữ nghĩa thời gian thực). Khác với phần mềm truyền thống nơi tính đúng đắn gắn liền với mã trạng thái và cấu trúc dữ liệu, các mô hình ngôn ngữ lớn có thể sinh mã 200 nhưng nội dung hoàn toàn sai lệch thực tế. Do đó, hệ sinh thái giám sát hiện đại bắt buộc phải tích hợp LLM-as-a-judge, NLI scoring, và tín hiệu phản hồi hành vi người dùng vào cùng dashboard vận hành.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangSmith Documentation: Online Evaluation in Production (https://docs.smith.langchain.com/evaluation) &amp; Datadog LLM Observability Guide</t>
         </is>
       </c>
     </row>
@@ -1182,10 +1250,29 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Performance, Reliability.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Performance, Reliability.</t>
+- 1.0đ: Định nghĩa họ Performance/Latency với các chỉ số chuẩn (P95, TTFT) và nhận định trạng thái trong bối cảnh.
+- 1.0đ: Định nghĩa họ Reliability/Execution với chỉ số kỹ thuật và chỉ rõ lỗi schema tool 12% dù HTTP 200.
+- 1.0đ: Định nghĩa họ Quality/Correctness và liên hệ sự sụt giảm groundedness/tính chính xác.
+- 1.0đ: Định nghĩa họ Cost/Resource (token tăng 4x do retry) và nêu nguyên tắc cấm gộp composite score làm mất góc nhìn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết lập Metric Contract phân định nghiêm ngặt 4 họ chỉ số độc lập, tuyệt đối không gộp chung:
+1. **Performance / Latency Family** (Đo lường thời gian đáp ứng):
+- Metrics: `agent_request_duration_seconds` (P50, P95, P99), `time_to_first_token_seconds` (TTFT), `token_generation_throughput_tps`.
+- Tình trạng: Đang ở mức tốt/thấp; phản ánh hạ tầng xử lý nhanh nhưng không bảo đảm độ chính xác.
+2. **Reliability / Execution Family** (Đo lường tính toàn vẹn kỹ thuật):
+- Metrics: `http_status_5xx_rate` (0%), `tool_call_schema_failure_rate` (12%), `tool_retry_count`, `unhandled_exception_total`.
+- Tình trạng: HTTP đạt 200 OK nhưng tầng tool execution bị suy thoái nghiêm trọng với 12% schema failure, làm đứt gãy luồng xử lý của agent.
+3. **Quality / Correctness Family** (Đo lường giá trị ngữ nghĩa):
+- Metrics: `groundedness_score`, `faithfulness_ratio`, `task_completion_rate`, `user_negative_feedback_rate`.
+- Tình trạng: Điểm groundedness giảm sâu; câu trả lời không có căn cứ dù trả về nhanh và không sập app.
+4. **Cost / Resource Family** (Đo lường tài nguyên tiêu thụ):
+- Metrics: `prompt_tokens_per_task`, `completion_tokens_per_task` (tăng gấp 4 lần), `cost_per_successful_resolution_usd`, `cache_hit_rate`.
+- Tình trạng: Chi phí tăng vọt 4× do agent phải lặp lại vòng lặp suy luận và retry sau khi tool call schema thất bại.
+5. **Nguyên tắc Contract**: Mỗi họ metric sở hữu SLO và cảnh báo riêng biệt. Cấm tạo composite score trung bình số học vì sẽ che giấu sự đánh đổi tiêu cực giữa latency nhanh và chất lượng kém/chi phí cao.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc tách biệt họ chỉ số (Metric Family Separation): Trong kiến trúc Agentic AI, một request có thể thành công về mặt HTTP nhưng thất bại về mặt nghiệp vụ. Việc trộn lẫn các khía cạnh này thành một điểm số tổng hợp duy nhất sẽ gây ngộ nhận nguy hiểm (ví dụ: latency giảm làm tăng điểm tổng, che lấp sự bùng nổ 400% chi phí token và sự sụt giảm căn cứ dữ liệu). Một hợp đồng metric chuẩn mực phải giữ nguyên 4 chiều độc lập để cung cấp đầy đủ thông tin cho các bên liên quan.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Semantic Conventions for Generative AI Systems (https://opentelemetry.io/docs/specs/semconv/gen-ai/) &amp; Google SRE Workbook</t>
         </is>
       </c>
     </row>
@@ -1268,10 +1355,26 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra RED rate/errors/duration, USE utilization/saturation/errors.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra RED rate/errors/duration, USE utilization/saturation/errors.</t>
+- 1.0đ: Chọn đầy đủ và chuẩn xác các chỉ số RED cho route `/chat` (Rate, Errors, Duration P95).
+- 1.0đ: Chọn đầy đủ và chuẩn xác các chỉ số USE cho tài nguyên (GPU Utilization, Queue Saturation, Errors).
+- 1.0đ: Trình bày các bước xác nhận logic (tách queue time vs execution time, kiểm tra batching/concurrency lock).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn chỉ số theo RED và USE:
+- **RED View (Tập trung vào Request / Dịch vụ `/chat`)**:
+  + Rate: `sum(rate(http_requests_total{route='/chat'}[5m]))` - Tần suất request vào endpoint chat.
+  + Errors: `sum(rate(http_requests_errors_total{route='/chat'}[5m]))` - Số lượng lỗi phát sinh.
+  + Duration: `histogram_quantile(0.95, sum(rate(http_request_duration_seconds_bucket{route='/chat'}[5m])) by (le))` - Thời gian phản hồi P95 của route `/chat`.
+- **USE View (Tập trung vào Tài nguyên / Infrastructure &amp; Serving Engine)**:
+  + Utilization: `gpu_utilization_percent` - Thời gian GPU bận rộn xử lý compute (hiện tại bình thường).
+  + Saturation: `model_serving_queue_depth` hoặc `pending_requests_count` - Mức độ ứ đọng hàng đợi (hiện tại đang cao bất thường).
+  + Errors: `gpu_memory_allocation_failures` hoặc `dropped_requests_total`.
+2. Các bước xác nhận nguyên nhân gốc (Verification Steps):
+- **Bước 1: Tách thời gian chờ và thời gian xử lý**: Bổ sung instrumentation đo lường `queue_wait_duration_seconds` so với `inference_execution_duration_seconds`. Nếu 80%+ thời gian P95 nằm ở thời gian chờ hàng đợi, xác nhận nghẽn do cơ chế điều phối/concurrency.
+- **Bước 2: Kiểm tra cấu hình Batching &amp; Concurrency Limit**: Đối soát các tham số `max_batch_size`, `max_waiting_tokens`, hoặc mutex lock trong service gateway `/chat`. Queue saturation cao khi GPU utilization bình thường chứng minh server đang bị nghẽn ở thread pool CPU, locking contention, hoặc batching timeout quá dài trước khi dispatch lệnh cho GPU.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phương pháp RED (Rate, Errors, Duration) phục vụ việc đánh giá trải nghiệm người dùng đối với các dịch vụ hướng request. Phương pháp USE (Utilization, Saturation, Errors) phục vụ việc phân tích trạng thái các tài nguyên hạ tầng (CPU, GPU, Memory, Network). Khi một route bị tăng P95 và tài nguyên tính toán không bận (low utilization) nhưng hàng đợi đầy (high saturation), nút thắt cổ chai không nằm ở phần cứng mà nằm ở lớp phần mềm điều phối (concurrency limits, thread exhaustion, hoặc scheduler bottleneck).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Brendan Gregg: The USE Method (https://www.brendangregg.com/usemethod.html) &amp; Tom Wilkie: The RED Method (https://grafana.com/blog/2018/08/02/the-red-method-how-to-instrument-your-services/)</t>
         </is>
       </c>
     </row>
@@ -1350,10 +1453,22 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Median, P95/P99 tail.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Median, P95/P99 tail.</t>
+- 1.0đ: Lựa chọn chính xác Release A và lập luận chặt chẽ trên cả hai tiêu chí mục tiêu.
+- 1.0đ: Phân tích sâu sự khác biệt giữa Mean và Percentile, chỉ rõ hiện tượng long-tail lag nghiêm trọng của B (P95=8s).
+- 1.0đ: Phân tích ưu thế của TTFT 0.5s ở Release A đối với trải nghiệm streaming UI.
+- 1.0đ: Nêu rõ các giới hạn quan sát thực tế (Inter-Token Latency, rủi ro câu trả lời bị cắt ngắn, chi phí phần cứng).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Release tối ưu: **Chọn Release A**.
+- **Phản hồi sớm (TTFT - Time to First Token)**: Release A có TTFT P95 là 0.5s, nhanh hơn 4 lần so với Release B (2.0s). Đối với ứng dụng AI có streaming giao diện, TTFT là yếu tố sống còn quyết định cảm giác mượt mà của người dùng khi nhìn thấy câu trả lời xuất hiện tức thì.
+- **Kiểm soát Tail Lag (P95 Latency)**: Release A có P95 là 3s, trong khi Release B lên tới 8s. Mặc dù cả hai có cùng Mean (2s), nhưng phân phối thời gian của B có đuôi rất dài (long-tail lag nặng nề). Với B, có tới 5% người dùng phải chịu đựng thời gian chờ từ 8 giây trở lên, gây trải nghiệm rất xấu.
+2. Giới hạn của mô hình và rủi ro cần kiểm chứng:
+- **Inter-Token Latency (ITL / TPS)**: TTFT nhanh chỉ chứng minh token đầu tiên xuất hiện sớm, chưa chứng minh tốc độ sinh các token tiếp theo có đều đặn hay không; nếu Release A bị giật cục sau token đầu, trải nghiệm người dùng vẫn bị tổn hại.
+- **Độ dài câu trả lời (Output Length Contamination)**: Cần kiểm tra xem P95 của Release A thấp có phải do model sinh câu trả lời quá ngắn hoặc bị ngắt sớm (premature termination) hay không.
+- **Chi phí tài nguyên (Over-provisioning Cost)**: Release A có thể đạt được TTFT và P95 tốt nhờ duy trì lượng GPU dự phòng lớn (speculative decoding / high concurrency), có thể dẫn đến chi phí vận hành hạ tầng cao hơn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chỉ số trung bình (Mean Latency) là một 'cạm bẫy' kinh điển trong giám sát hiệu năng vì nó che giấu hoàn toàn phân phối đuôi (tail percentiles). Hai phiên bản có cùng mean 2s có thể mang lại trải nghiệm hoàn toàn trái ngược: Release A phân bổ đều quanh mốc trung bình, trong khi Release B phân hóa nghiêm trọng với P95 lên đến 8s. Kết hợp với TTFT (Time to First Token) - chỉ số đo lường độ phản ứng tức thì của LLM streaming - Release A vượt trội hoàn toàn theo tiêu chí 'phản hồi sớm và ít tail lag'.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Service Level Objectives (https://sre.google/sre-book/service-level-objectives/) &amp; vLLM Metrics Documentation (https://docs.vllm.ai)</t>
         </is>
       </c>
     </row>
